--- a/app/reports/BIVI_research.xlsx
+++ b/app/reports/BIVI_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.0472</v>
+        <v>0.04719999790191651</v>
       </c>
     </row>
     <row r="6">
@@ -1559,7 +1559,7 @@
         <v>0.00013079667</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>-0.958</v>
+        <v>-0.96</v>
       </c>
       <c r="F8" s="33" t="n"/>
     </row>
